--- a/AAII_Financials/Quarterly/AVVIY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AVVIY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="409" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="455" uniqueCount="92">
   <si>
     <t>AVVIY</t>
   </si>
@@ -656,74 +656,80 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="17" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="19" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -769,8 +775,14 @@
       <c r="Q8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -816,8 +828,14 @@
       <c r="Q9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -863,8 +881,14 @@
       <c r="Q10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -882,8 +906,10 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -929,8 +955,14 @@
       <c r="Q12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -976,8 +1008,14 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1023,8 +1061,14 @@
       <c r="Q14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1070,8 +1114,14 @@
       <c r="Q15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1086,8 +1136,10 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1133,8 +1185,14 @@
       <c r="Q17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1180,8 +1238,14 @@
       <c r="Q18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1199,8 +1263,10 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1246,8 +1312,14 @@
       <c r="Q20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1293,8 +1365,14 @@
       <c r="Q21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1340,8 +1418,14 @@
       <c r="Q22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1387,8 +1471,14 @@
       <c r="Q23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1434,8 +1524,14 @@
       <c r="Q24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1481,8 +1577,14 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1528,8 +1630,14 @@
       <c r="Q26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1575,8 +1683,14 @@
       <c r="Q27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1622,8 +1736,14 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1669,8 +1789,14 @@
       <c r="Q29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1716,8 +1842,14 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1763,8 +1895,14 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1810,8 +1948,14 @@
       <c r="Q32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1857,8 +2001,14 @@
       <c r="Q33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1904,8 +2054,14 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1951,60 +2107,72 @@
       <c r="Q35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2022,8 +2190,10 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2041,55 +2211,63 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>28126600</v>
+      </c>
+      <c r="E41" s="3">
+        <v>27992700</v>
+      </c>
+      <c r="F41" s="3">
         <v>24495300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>24464300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>27346200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>25788400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>29290000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>31357700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>21418700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>21404900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>22001600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>21078500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>25207500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>24539800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>27116100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>25077200</v>
       </c>
     </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2135,55 +2313,67 @@
       <c r="Q42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R42" s="3">
+        <v>0</v>
+      </c>
+      <c r="S42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>8634700</v>
+      </c>
+      <c r="E43" s="3">
+        <v>8593600</v>
+      </c>
+      <c r="F43" s="3">
         <v>6901700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>6893000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>6570800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>6196500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>4956400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>5306300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>6267100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>6263100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>4860700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>4656700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>4939600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>4808700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>4597900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>4252100</v>
       </c>
     </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2229,243 +2419,279 @@
       <c r="Q44" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S44" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>23481500</v>
+      </c>
+      <c r="E45" s="3">
+        <v>23369700</v>
+      </c>
+      <c r="F45" s="3">
         <v>23742900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>23712900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>20011000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>18871000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>18753800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>20077700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>17097800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>17086800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>16769000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>16065500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>14785700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>14394100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>14518900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>13427200</v>
       </c>
     </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>64874600</v>
+      </c>
+      <c r="E46" s="3">
+        <v>64565800</v>
+      </c>
+      <c r="F46" s="3">
         <v>59558500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>59483300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>58635400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>55295300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>57309400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>61355000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>49127400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>49095700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>47951800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>45940000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>49061500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>47762000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>49633100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>45901100</v>
       </c>
     </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>427309300</v>
+      </c>
+      <c r="E47" s="3">
+        <v>425275200</v>
+      </c>
+      <c r="F47" s="3">
         <v>410091500</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>409573400</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>375413100</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>354027800</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>332103100</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>355547500</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>335499900</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>335283800</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>314846900</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>301637700</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>296398600</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>288547900</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>272220000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>251751100</v>
       </c>
     </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>682000</v>
+      </c>
+      <c r="E48" s="3">
+        <v>678700</v>
+      </c>
+      <c r="F48" s="3">
         <v>707900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>707000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>517900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>488400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>444400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>475800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>527000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>526700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>540100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>517400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>491800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>478800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>421700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>390000</v>
       </c>
     </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>9571400</v>
+      </c>
+      <c r="E49" s="3">
+        <v>9525900</v>
+      </c>
+      <c r="F49" s="3">
         <v>9877500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>9865000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>6200800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>5847600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>5678700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>6079600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>5436800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>5433300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>4911600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>4705500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>4826500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>4698600</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>4775000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>4415900</v>
       </c>
     </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2511,8 +2737,14 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2558,55 +2790,67 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>10391400</v>
+      </c>
+      <c r="E52" s="3">
+        <v>10341900</v>
+      </c>
+      <c r="F52" s="3">
         <v>10205900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>10193000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>9815000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>9255900</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>8480500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>9079200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>9167500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>9161600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>9036000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>8656900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>9031500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>8792300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>8594500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>7948300</v>
       </c>
     </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2652,55 +2896,67 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>552976000</v>
+      </c>
+      <c r="E54" s="3">
+        <v>550343700</v>
+      </c>
+      <c r="F54" s="3">
         <v>532037700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>531365400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>496152900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>467889800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>443034900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>474310400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>440402100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>440118500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>418865600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>401292300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>399717900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>389130500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>373014000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>344966200</v>
       </c>
     </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2718,8 +2974,10 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2737,8 +2995,10 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -2784,243 +3044,279 @@
       <c r="Q57" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S57" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>67700</v>
+      </c>
+      <c r="E58" s="3">
+        <v>67300</v>
+      </c>
+      <c r="F58" s="3">
         <v>8795400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>8784300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>69900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>65900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>9363100</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>10024100</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>63200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>63100</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>7771200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>7445100</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>514700</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>501000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>722900</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>668600</v>
       </c>
     </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>22799500</v>
+      </c>
+      <c r="E59" s="3">
+        <v>22691000</v>
+      </c>
+      <c r="F59" s="3">
         <v>27106300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>27072100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>22511300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>21229000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>24417500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>26141300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>22615500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>22601000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>21162200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>20274300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>19061900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>18557000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>17367300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>16061400</v>
       </c>
     </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>22867200</v>
+      </c>
+      <c r="E60" s="3">
+        <v>22758300</v>
+      </c>
+      <c r="F60" s="3">
         <v>38768500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>38719500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>22581200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>21294800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>36247000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>38805800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>22678700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>22664100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>31564900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>30240600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>19576600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>19058000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>20130100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>18616500</v>
       </c>
     </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>7968700</v>
+      </c>
+      <c r="E61" s="3">
+        <v>7930800</v>
+      </c>
+      <c r="F61" s="3">
         <v>7938100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>7928100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>8308000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>7834700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>7303700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>7819300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>7953000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>7947900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>8429700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>8076100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>7823000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>7615800</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>7881200</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>7288600</v>
       </c>
     </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>507355700</v>
+      </c>
+      <c r="E62" s="3">
+        <v>504940500</v>
+      </c>
+      <c r="F62" s="3">
         <v>469192500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>468599600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>452551000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>426771700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>387742400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>415114600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>396749500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>396494000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>365444300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>350112300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>358865700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>349360400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>331333200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>306419400</v>
       </c>
     </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3066,8 +3362,14 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3113,8 +3415,14 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3160,55 +3468,67 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>539741300</v>
+      </c>
+      <c r="E66" s="3">
+        <v>537171900</v>
+      </c>
+      <c r="F66" s="3">
         <v>517113100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>516459700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>484540300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>456938700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>432242100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>462755700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>428453000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>428177000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>406637500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>389577300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>387359400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>377099400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>360707300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>333584800</v>
       </c>
     </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3226,8 +3546,10 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3273,8 +3595,14 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3320,8 +3648,14 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3338,37 +3672,43 @@
         <v>0</v>
       </c>
       <c r="H70" s="3">
+        <v>0</v>
+      </c>
+      <c r="I70" s="3">
+        <v>0</v>
+      </c>
+      <c r="J70" s="3">
         <v>250400</v>
       </c>
-      <c r="I70" s="3">
+      <c r="K70" s="3">
         <v>268100</v>
       </c>
-      <c r="J70" s="3">
+      <c r="L70" s="3">
         <v>252800</v>
       </c>
-      <c r="K70" s="3">
+      <c r="M70" s="3">
         <v>252600</v>
       </c>
-      <c r="L70" s="3">
+      <c r="N70" s="3">
         <v>254800</v>
       </c>
-      <c r="M70" s="3">
+      <c r="O70" s="3">
         <v>244100</v>
       </c>
-      <c r="N70" s="3">
+      <c r="P70" s="3">
         <v>254200</v>
       </c>
-      <c r="O70" s="3">
+      <c r="Q70" s="3">
         <v>247400</v>
       </c>
-      <c r="P70" s="3">
+      <c r="R70" s="3">
         <v>241000</v>
       </c>
-      <c r="Q70" s="3">
+      <c r="S70" s="3">
         <v>222900</v>
       </c>
     </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3414,55 +3754,67 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>591700</v>
+      </c>
+      <c r="E72" s="3">
+        <v>588900</v>
+      </c>
+      <c r="F72" s="3">
         <v>1650100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>1648000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>1837200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>1732600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>1737700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>1860300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>2685600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>2683800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>2837900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>2718900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>2963500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>2885000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-2805000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-2594100</v>
       </c>
     </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3508,8 +3860,14 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3555,8 +3913,14 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3602,55 +3966,67 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+      <c r="S75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>13137900</v>
+      </c>
+      <c r="E76" s="3">
+        <v>13075300</v>
+      </c>
+      <c r="F76" s="3">
         <v>14382200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>14364100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>11529000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>10872200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>10146900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>10863200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>11294500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>11287200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>11568200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>11082900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>11705300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>11395200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>11692300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>10813100</v>
       </c>
     </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3696,60 +4072,72 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+      <c r="S77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -3795,8 +4183,14 @@
       <c r="Q81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3814,55 +4208,63 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
+      <c r="D83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F83" s="3">
         <v>38800</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>41500</v>
       </c>
-      <c r="F83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H83" s="3">
+      <c r="H83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J83" s="3">
         <v>42700</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>40900</v>
       </c>
-      <c r="J83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L83" s="3">
+      <c r="L83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N83" s="3">
         <v>34300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>31800</v>
       </c>
-      <c r="N83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P83" s="3">
+      <c r="P83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R83" s="3">
         <v>50100</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>50000</v>
       </c>
     </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3908,8 +4310,14 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3955,8 +4363,14 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4002,8 +4416,14 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4049,8 +4469,14 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+      <c r="S87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4096,55 +4522,67 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>2975300</v>
+      </c>
+      <c r="E89" s="3">
+        <v>2961200</v>
+      </c>
+      <c r="F89" s="3">
         <v>378200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>377700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-2140700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-2018800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>4840600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>5182300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>449900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>449600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-994200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-952500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-744000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-724300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>5958200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>5510200</v>
       </c>
     </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4162,55 +4600,63 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-27900</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-27700</v>
+      </c>
+      <c r="F91" s="3">
         <v>-43100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-43000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-19900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-18700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-10000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-10700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-21500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-21500</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-54800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-52500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-40000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-39000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-6000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-5600</v>
       </c>
     </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4256,8 +4702,14 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+      <c r="S92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4303,55 +4755,67 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>176500</v>
+      </c>
+      <c r="E94" s="3">
+        <v>175600</v>
+      </c>
+      <c r="F94" s="3">
         <v>-715300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-714400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-54100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-51000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-87000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-93200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>190200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>190100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-182800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-175100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-40000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-39000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-189200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-174900</v>
       </c>
     </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4369,55 +4833,63 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>555300</v>
+      </c>
+      <c r="E96" s="3">
+        <v>552600</v>
+      </c>
+      <c r="F96" s="3">
         <v>293400</v>
       </c>
-      <c r="E96" s="3">
+      <c r="G96" s="3">
         <v>293000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="H96" s="3">
         <v>446600</v>
       </c>
-      <c r="G96" s="3">
+      <c r="I96" s="3">
         <v>421200</v>
       </c>
-      <c r="H96" s="3">
+      <c r="J96" s="3">
         <v>209700</v>
       </c>
-      <c r="I96" s="3">
+      <c r="K96" s="3">
         <v>224500</v>
       </c>
-      <c r="J96" s="3">
+      <c r="L96" s="3">
         <v>391800</v>
       </c>
-      <c r="K96" s="3">
+      <c r="M96" s="3">
         <v>391500</v>
       </c>
-      <c r="L96" s="3">
+      <c r="N96" s="3">
         <v>203200</v>
       </c>
-      <c r="M96" s="3">
+      <c r="O96" s="3">
         <v>194600</v>
       </c>
-      <c r="N96" s="3">
+      <c r="P96" s="3">
         <v>376800</v>
       </c>
-      <c r="O96" s="3">
+      <c r="Q96" s="3">
         <v>366800</v>
       </c>
-      <c r="P96" s="3">
+      <c r="R96" s="3">
         <v>183100</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="S96" s="3">
         <v>169400</v>
       </c>
     </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4463,8 +4935,14 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4510,8 +4988,14 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4557,145 +5041,169 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+      <c r="S99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-897600</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-893300</v>
+      </c>
+      <c r="F100" s="3">
         <v>-989200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-988000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-388400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-366300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-846300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-906000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-721600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-721200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-408200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-391100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-749100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-729300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-561500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>-519300</v>
       </c>
     </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-21200</v>
+      </c>
+      <c r="E101" s="3">
+        <v>-20000</v>
+      </c>
+      <c r="F101" s="3">
         <v>-132100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>-141400</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>-600</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>-600</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>27400</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>26200</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>-41300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>-40200</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>12700</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>11700</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>43700</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>47300</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>-12200</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="S101" s="3">
         <v>-12200</v>
       </c>
     </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>2205100</v>
+      </c>
+      <c r="E102" s="3">
+        <v>2194600</v>
+      </c>
+      <c r="F102" s="3">
         <v>-1164200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-1162700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-2604500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-2456100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>3775200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>4041700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-82100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-82100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-1557800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-1492400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-1574500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-1532800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>5220200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>4827700</v>
       </c>
     </row>
